--- a/sales_data.xlsx
+++ b/sales_data.xlsx
@@ -52,13 +52,40 @@
     <t>平板</t>
   </si>
   <si>
-    <t>2026-01-20</t>
-  </si>
-  <si>
     <t>无人机</t>
   </si>
   <si>
     <t>哈雷</t>
+  </si>
+  <si>
+    <t>AAA</t>
+  </si>
+  <si>
+    <t>张</t>
+  </si>
+  <si>
+    <t>BBB</t>
+  </si>
+  <si>
+    <t>江</t>
+  </si>
+  <si>
+    <t>CCC</t>
+  </si>
+  <si>
+    <t>黄</t>
+  </si>
+  <si>
+    <t>DDD</t>
+  </si>
+  <si>
+    <t>戴</t>
+  </si>
+  <si>
+    <t>EEE</t>
+  </si>
+  <si>
+    <t>杨</t>
   </si>
 </sst>
 </file>
@@ -161,7 +188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -187,9 +214,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -512,7 +536,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.9990234375" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="6.375"/>
+    <col min="1" max="1" width="9"/>
+    <col min="2" max="2" width="6.375"/>
     <col min="3" max="3" width="13.3740234375"/>
     <col min="4" max="4" width="8.1240234375"/>
     <col min="5" max="5" width="9.375"/>
@@ -753,11 +778,11 @@
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>12</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>13</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>66</v>
@@ -766,17 +791,117 @@
         <v>1000</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="8" t="n">
         <v>66666</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1"/>
-    <row r="14" ht="16.5" customHeight="1"/>
-    <row r="15" ht="16.5" customHeight="1"/>
-    <row r="16" ht="16.5" customHeight="1"/>
-    <row r="17" ht="16.5" customHeight="1"/>
+    <row r="13" ht="16.5" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <f>C13*D13</f>
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <f>C14*D14</f>
+        <v>22200</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>333</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <f>C15*D15</f>
+        <v>33300</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>444</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <f>C16*D16</f>
+        <v>44400</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>555</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <f>C17*D17</f>
+        <v>55500</v>
+      </c>
+    </row>
     <row r="18" ht="16.5" customHeight="1"/>
     <row r="19" ht="16.5" customHeight="1"/>
     <row r="20" ht="16.5" customHeight="1"/>
